--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C904"/>
+  <dimension ref="A1:C905"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10336,6 +10336,17 @@
       </c>
       <c r="C904">
         <v>86.3793</v>
+      </c>
+    </row>
+    <row r="905" spans="1:3">
+      <c r="A905" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B905">
+        <v>1</v>
+      </c>
+      <c r="C905">
+        <v>86.753</v>
       </c>
     </row>
   </sheetData>
@@ -10345,7 +10356,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C904"/>
+  <dimension ref="A1:C905"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20290,6 +20301,17 @@
       </c>
       <c r="C904">
         <v>100.5714</v>
+      </c>
+    </row>
+    <row r="905" spans="1:3">
+      <c r="A905" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B905">
+        <v>1</v>
+      </c>
+      <c r="C905">
+        <v>100.5988</v>
       </c>
     </row>
   </sheetData>
@@ -20299,7 +20321,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C904"/>
+  <dimension ref="A1:C905"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -30244,6 +30266,17 @@
       </c>
       <c r="C904">
         <v>61.8994</v>
+      </c>
+    </row>
+    <row r="905" spans="1:3">
+      <c r="A905" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B905">
+        <v>1</v>
+      </c>
+      <c r="C905">
+        <v>62.2019</v>
       </c>
     </row>
   </sheetData>
@@ -30253,7 +30286,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C904"/>
+  <dimension ref="A1:C905"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -40198,6 +40231,17 @@
       </c>
       <c r="C904">
         <v>12.858</v>
+      </c>
+    </row>
+    <row r="905" spans="1:3">
+      <c r="A905" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B905">
+        <v>1</v>
+      </c>
+      <c r="C905">
+        <v>12.897</v>
       </c>
     </row>
   </sheetData>
@@ -40207,7 +40251,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C904"/>
+  <dimension ref="A1:C905"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -50152,6 +50196,17 @@
       </c>
       <c r="C904">
         <v>117.3204</v>
+      </c>
+    </row>
+    <row r="905" spans="1:3">
+      <c r="A905" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B905">
+        <v>1</v>
+      </c>
+      <c r="C905">
+        <v>117.7325</v>
       </c>
     </row>
   </sheetData>
@@ -50161,7 +50216,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C904"/>
+  <dimension ref="A1:C905"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -60106,6 +60161,17 @@
       </c>
       <c r="C904">
         <v>18.5854</v>
+      </c>
+    </row>
+    <row r="905" spans="1:3">
+      <c r="A905" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B905">
+        <v>100</v>
+      </c>
+      <c r="C905">
+        <v>18.7651</v>
       </c>
     </row>
   </sheetData>
@@ -60115,7 +60181,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C904"/>
+  <dimension ref="A1:C905"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -70060,6 +70126,17 @@
       </c>
       <c r="C904">
         <v>53.9837</v>
+      </c>
+    </row>
+    <row r="905" spans="1:3">
+      <c r="A905" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B905">
+        <v>100</v>
+      </c>
+      <c r="C905">
+        <v>54.2987</v>
       </c>
     </row>
   </sheetData>
@@ -70069,7 +70146,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C904"/>
+  <dimension ref="A1:C905"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -80016,6 +80093,17 @@
         <v>106.7993</v>
       </c>
     </row>
+    <row r="905" spans="1:3">
+      <c r="A905" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B905">
+        <v>1</v>
+      </c>
+      <c r="C905">
+        <v>107.0892</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C905"/>
+  <dimension ref="A1:C906"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10347,6 +10347,17 @@
       </c>
       <c r="C905">
         <v>86.753</v>
+      </c>
+    </row>
+    <row r="906" spans="1:3">
+      <c r="A906" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B906">
+        <v>1</v>
+      </c>
+      <c r="C906">
+        <v>86.99630000000001</v>
       </c>
     </row>
   </sheetData>
@@ -10356,7 +10367,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C905"/>
+  <dimension ref="A1:C906"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20312,6 +20323,17 @@
       </c>
       <c r="C905">
         <v>100.5988</v>
+      </c>
+    </row>
+    <row r="906" spans="1:3">
+      <c r="A906" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B906">
+        <v>1</v>
+      </c>
+      <c r="C906">
+        <v>100.8287</v>
       </c>
     </row>
   </sheetData>
@@ -20321,7 +20343,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C905"/>
+  <dimension ref="A1:C906"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -30277,6 +30299,17 @@
       </c>
       <c r="C905">
         <v>62.2019</v>
+      </c>
+    </row>
+    <row r="906" spans="1:3">
+      <c r="A906" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B906">
+        <v>1</v>
+      </c>
+      <c r="C906">
+        <v>62.1415</v>
       </c>
     </row>
   </sheetData>
@@ -30286,7 +30319,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C905"/>
+  <dimension ref="A1:C906"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -40242,6 +40275,17 @@
       </c>
       <c r="C905">
         <v>12.897</v>
+      </c>
+    </row>
+    <row r="906" spans="1:3">
+      <c r="A906" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B906">
+        <v>1</v>
+      </c>
+      <c r="C906">
+        <v>12.9217</v>
       </c>
     </row>
   </sheetData>
@@ -40251,7 +40295,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C905"/>
+  <dimension ref="A1:C906"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -50207,6 +50251,17 @@
       </c>
       <c r="C905">
         <v>117.7325</v>
+      </c>
+    </row>
+    <row r="906" spans="1:3">
+      <c r="A906" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B906">
+        <v>1</v>
+      </c>
+      <c r="C906">
+        <v>117.7756</v>
       </c>
     </row>
   </sheetData>
@@ -50216,7 +50271,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C905"/>
+  <dimension ref="A1:C906"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -60172,6 +60227,17 @@
       </c>
       <c r="C905">
         <v>18.7651</v>
+      </c>
+    </row>
+    <row r="906" spans="1:3">
+      <c r="A906" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B906">
+        <v>100</v>
+      </c>
+      <c r="C906">
+        <v>18.9762</v>
       </c>
     </row>
   </sheetData>
@@ -60181,7 +60247,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C905"/>
+  <dimension ref="A1:C906"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -70137,6 +70203,17 @@
       </c>
       <c r="C905">
         <v>54.2987</v>
+      </c>
+    </row>
+    <row r="906" spans="1:3">
+      <c r="A906" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B906">
+        <v>100</v>
+      </c>
+      <c r="C906">
+        <v>54.2879</v>
       </c>
     </row>
   </sheetData>
@@ -70146,7 +70223,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C905"/>
+  <dimension ref="A1:C906"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -80104,6 +80181,17 @@
         <v>107.0892</v>
       </c>
     </row>
+    <row r="906" spans="1:3">
+      <c r="A906" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B906">
+        <v>1</v>
+      </c>
+      <c r="C906">
+        <v>106.757</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C906"/>
+  <dimension ref="A1:C907"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10358,6 +10358,17 @@
       </c>
       <c r="C906">
         <v>86.99630000000001</v>
+      </c>
+    </row>
+    <row r="907" spans="1:3">
+      <c r="A907" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B907">
+        <v>1</v>
+      </c>
+      <c r="C907">
+        <v>86.88720000000001</v>
       </c>
     </row>
   </sheetData>
@@ -10367,7 +10378,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C906"/>
+  <dimension ref="A1:C907"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20334,6 +20345,17 @@
       </c>
       <c r="C906">
         <v>100.8287</v>
+      </c>
+    </row>
+    <row r="907" spans="1:3">
+      <c r="A907" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B907">
+        <v>1</v>
+      </c>
+      <c r="C907">
+        <v>100.598</v>
       </c>
     </row>
   </sheetData>
@@ -20343,7 +20365,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C906"/>
+  <dimension ref="A1:C907"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -30310,6 +30332,17 @@
       </c>
       <c r="C906">
         <v>62.1415</v>
+      </c>
+    </row>
+    <row r="907" spans="1:3">
+      <c r="A907" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B907">
+        <v>1</v>
+      </c>
+      <c r="C907">
+        <v>62.246</v>
       </c>
     </row>
   </sheetData>
@@ -30319,7 +30352,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C906"/>
+  <dimension ref="A1:C907"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -40286,6 +40319,17 @@
       </c>
       <c r="C906">
         <v>12.9217</v>
+      </c>
+    </row>
+    <row r="907" spans="1:3">
+      <c r="A907" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B907">
+        <v>1</v>
+      </c>
+      <c r="C907">
+        <v>12.9191</v>
       </c>
     </row>
   </sheetData>
@@ -40295,7 +40339,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C906"/>
+  <dimension ref="A1:C907"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -50262,6 +50306,17 @@
       </c>
       <c r="C906">
         <v>117.7756</v>
+      </c>
+    </row>
+    <row r="907" spans="1:3">
+      <c r="A907" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B907">
+        <v>1</v>
+      </c>
+      <c r="C907">
+        <v>117.3499</v>
       </c>
     </row>
   </sheetData>
@@ -50271,7 +50326,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C906"/>
+  <dimension ref="A1:C907"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -60238,6 +60293,17 @@
       </c>
       <c r="C906">
         <v>18.9762</v>
+      </c>
+    </row>
+    <row r="907" spans="1:3">
+      <c r="A907" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B907">
+        <v>100</v>
+      </c>
+      <c r="C907">
+        <v>19.0793</v>
       </c>
     </row>
   </sheetData>
@@ -60247,7 +60313,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C906"/>
+  <dimension ref="A1:C907"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -70214,6 +70280,17 @@
       </c>
       <c r="C906">
         <v>54.2879</v>
+      </c>
+    </row>
+    <row r="907" spans="1:3">
+      <c r="A907" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B907">
+        <v>100</v>
+      </c>
+      <c r="C907">
+        <v>54.9919</v>
       </c>
     </row>
   </sheetData>
@@ -70223,7 +70300,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C906"/>
+  <dimension ref="A1:C907"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -80192,6 +80269,17 @@
         <v>106.757</v>
       </c>
     </row>
+    <row r="907" spans="1:3">
+      <c r="A907" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B907">
+        <v>1</v>
+      </c>
+      <c r="C907">
+        <v>107.4273</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C907"/>
+  <dimension ref="A1:C908"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10369,6 +10369,17 @@
       </c>
       <c r="C907">
         <v>86.88720000000001</v>
+      </c>
+    </row>
+    <row r="908" spans="1:3">
+      <c r="A908" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B908">
+        <v>1</v>
+      </c>
+      <c r="C908">
+        <v>86.5857</v>
       </c>
     </row>
   </sheetData>
@@ -10378,7 +10389,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C907"/>
+  <dimension ref="A1:C908"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20356,6 +20367,17 @@
       </c>
       <c r="C907">
         <v>100.598</v>
+      </c>
+    </row>
+    <row r="908" spans="1:3">
+      <c r="A908" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B908">
+        <v>1</v>
+      </c>
+      <c r="C908">
+        <v>100.5693</v>
       </c>
     </row>
   </sheetData>
@@ -20365,7 +20387,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C907"/>
+  <dimension ref="A1:C908"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -30343,6 +30365,17 @@
       </c>
       <c r="C907">
         <v>62.246</v>
+      </c>
+    </row>
+    <row r="908" spans="1:3">
+      <c r="A908" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B908">
+        <v>1</v>
+      </c>
+      <c r="C908">
+        <v>62.4283</v>
       </c>
     </row>
   </sheetData>
@@ -30352,7 +30385,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C907"/>
+  <dimension ref="A1:C908"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -40330,6 +40363,17 @@
       </c>
       <c r="C907">
         <v>12.9191</v>
+      </c>
+    </row>
+    <row r="908" spans="1:3">
+      <c r="A908" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B908">
+        <v>1</v>
+      </c>
+      <c r="C908">
+        <v>12.8849</v>
       </c>
     </row>
   </sheetData>
@@ -40339,7 +40383,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C907"/>
+  <dimension ref="A1:C908"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -50317,6 +50361,17 @@
       </c>
       <c r="C907">
         <v>117.3499</v>
+      </c>
+    </row>
+    <row r="908" spans="1:3">
+      <c r="A908" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B908">
+        <v>1</v>
+      </c>
+      <c r="C908">
+        <v>117.0465</v>
       </c>
     </row>
   </sheetData>
@@ -50326,7 +50381,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C907"/>
+  <dimension ref="A1:C908"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -60304,6 +60359,17 @@
       </c>
       <c r="C907">
         <v>19.0793</v>
+      </c>
+    </row>
+    <row r="908" spans="1:3">
+      <c r="A908" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B908">
+        <v>100</v>
+      </c>
+      <c r="C908">
+        <v>18.9939</v>
       </c>
     </row>
   </sheetData>
@@ -60313,7 +60379,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C907"/>
+  <dimension ref="A1:C908"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -70291,6 +70357,17 @@
       </c>
       <c r="C907">
         <v>54.9919</v>
+      </c>
+    </row>
+    <row r="908" spans="1:3">
+      <c r="A908" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B908">
+        <v>100</v>
+      </c>
+      <c r="C908">
+        <v>55.5037</v>
       </c>
     </row>
   </sheetData>
@@ -70300,7 +70377,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C907"/>
+  <dimension ref="A1:C908"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -80280,6 +80357,17 @@
         <v>107.4273</v>
       </c>
     </row>
+    <row r="908" spans="1:3">
+      <c r="A908" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B908">
+        <v>1</v>
+      </c>
+      <c r="C908">
+        <v>107.0678</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C908"/>
+  <dimension ref="A1:C909"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10380,6 +10380,17 @@
       </c>
       <c r="C908">
         <v>86.5857</v>
+      </c>
+    </row>
+    <row r="909" spans="1:3">
+      <c r="A909" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B909">
+        <v>1</v>
+      </c>
+      <c r="C909">
+        <v>86.1909</v>
       </c>
     </row>
   </sheetData>
@@ -10389,7 +10400,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C908"/>
+  <dimension ref="A1:C909"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20378,6 +20389,17 @@
       </c>
       <c r="C908">
         <v>100.5693</v>
+      </c>
+    </row>
+    <row r="909" spans="1:3">
+      <c r="A909" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B909">
+        <v>1</v>
+      </c>
+      <c r="C909">
+        <v>100.1711</v>
       </c>
     </row>
   </sheetData>
@@ -20387,7 +20409,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C908"/>
+  <dimension ref="A1:C909"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -30376,6 +30398,17 @@
       </c>
       <c r="C908">
         <v>62.4283</v>
+      </c>
+    </row>
+    <row r="909" spans="1:3">
+      <c r="A909" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B909">
+        <v>1</v>
+      </c>
+      <c r="C909">
+        <v>62.135</v>
       </c>
     </row>
   </sheetData>
@@ -30385,7 +30418,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C908"/>
+  <dimension ref="A1:C909"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -40374,6 +40407,17 @@
       </c>
       <c r="C908">
         <v>12.8849</v>
+      </c>
+    </row>
+    <row r="909" spans="1:3">
+      <c r="A909" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B909">
+        <v>1</v>
+      </c>
+      <c r="C909">
+        <v>12.8537</v>
       </c>
     </row>
   </sheetData>
@@ -40383,7 +40427,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C908"/>
+  <dimension ref="A1:C909"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -50372,6 +50416,17 @@
       </c>
       <c r="C908">
         <v>117.0465</v>
+      </c>
+    </row>
+    <row r="909" spans="1:3">
+      <c r="A909" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B909">
+        <v>1</v>
+      </c>
+      <c r="C909">
+        <v>116.487</v>
       </c>
     </row>
   </sheetData>
@@ -50381,7 +50436,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C908"/>
+  <dimension ref="A1:C909"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -60370,6 +60425,17 @@
       </c>
       <c r="C908">
         <v>18.9939</v>
+      </c>
+    </row>
+    <row r="909" spans="1:3">
+      <c r="A909" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B909">
+        <v>100</v>
+      </c>
+      <c r="C909">
+        <v>18.8783</v>
       </c>
     </row>
   </sheetData>
@@ -60379,7 +60445,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C908"/>
+  <dimension ref="A1:C909"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -70368,6 +70434,17 @@
       </c>
       <c r="C908">
         <v>55.5037</v>
+      </c>
+    </row>
+    <row r="909" spans="1:3">
+      <c r="A909" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B909">
+        <v>100</v>
+      </c>
+      <c r="C909">
+        <v>55.2789</v>
       </c>
     </row>
   </sheetData>
@@ -70377,7 +70454,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C908"/>
+  <dimension ref="A1:C909"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -80368,6 +80445,17 @@
         <v>107.0678</v>
       </c>
     </row>
+    <row r="909" spans="1:3">
+      <c r="A909" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B909">
+        <v>1</v>
+      </c>
+      <c r="C909">
+        <v>106.4742</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C909"/>
+  <dimension ref="A1:C910"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10391,6 +10391,17 @@
       </c>
       <c r="C909">
         <v>86.1909</v>
+      </c>
+    </row>
+    <row r="910" spans="1:3">
+      <c r="A910" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B910">
+        <v>1</v>
+      </c>
+      <c r="C910">
+        <v>86.473</v>
       </c>
     </row>
   </sheetData>
@@ -10400,7 +10411,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C909"/>
+  <dimension ref="A1:C910"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20400,6 +20411,17 @@
       </c>
       <c r="C909">
         <v>100.1711</v>
+      </c>
+    </row>
+    <row r="910" spans="1:3">
+      <c r="A910" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B910">
+        <v>1</v>
+      </c>
+      <c r="C910">
+        <v>100.4989</v>
       </c>
     </row>
   </sheetData>
@@ -20409,7 +20431,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C909"/>
+  <dimension ref="A1:C910"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -30409,6 +30431,17 @@
       </c>
       <c r="C909">
         <v>62.135</v>
+      </c>
+    </row>
+    <row r="910" spans="1:3">
+      <c r="A910" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B910">
+        <v>1</v>
+      </c>
+      <c r="C910">
+        <v>62.4162</v>
       </c>
     </row>
   </sheetData>
@@ -30418,7 +30451,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C909"/>
+  <dimension ref="A1:C910"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -40418,6 +40451,17 @@
       </c>
       <c r="C909">
         <v>12.8537</v>
+      </c>
+    </row>
+    <row r="910" spans="1:3">
+      <c r="A910" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B910">
+        <v>1</v>
+      </c>
+      <c r="C910">
+        <v>12.8842</v>
       </c>
     </row>
   </sheetData>
@@ -40427,7 +40471,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C909"/>
+  <dimension ref="A1:C910"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -50427,6 +50471,17 @@
       </c>
       <c r="C909">
         <v>116.487</v>
+      </c>
+    </row>
+    <row r="910" spans="1:3">
+      <c r="A910" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B910">
+        <v>1</v>
+      </c>
+      <c r="C910">
+        <v>117.1277</v>
       </c>
     </row>
   </sheetData>
@@ -50436,7 +50491,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C909"/>
+  <dimension ref="A1:C910"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -60436,6 +60491,17 @@
       </c>
       <c r="C909">
         <v>18.8783</v>
+      </c>
+    </row>
+    <row r="910" spans="1:3">
+      <c r="A910" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B910">
+        <v>100</v>
+      </c>
+      <c r="C910">
+        <v>19.0339</v>
       </c>
     </row>
   </sheetData>
@@ -60445,7 +60511,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C909"/>
+  <dimension ref="A1:C910"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -70445,6 +70511,17 @@
       </c>
       <c r="C909">
         <v>55.2789</v>
+      </c>
+    </row>
+    <row r="910" spans="1:3">
+      <c r="A910" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B910">
+        <v>100</v>
+      </c>
+      <c r="C910">
+        <v>56.2609</v>
       </c>
     </row>
   </sheetData>
@@ -70454,7 +70531,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C909"/>
+  <dimension ref="A1:C910"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -80456,6 +80533,17 @@
         <v>106.4742</v>
       </c>
     </row>
+    <row r="910" spans="1:3">
+      <c r="A910" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B910">
+        <v>1</v>
+      </c>
+      <c r="C910">
+        <v>106.5201</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C910"/>
+  <dimension ref="A1:C911"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10402,6 +10402,17 @@
       </c>
       <c r="C910">
         <v>86.473</v>
+      </c>
+    </row>
+    <row r="911" spans="1:3">
+      <c r="A911" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B911">
+        <v>1</v>
+      </c>
+      <c r="C911">
+        <v>85.4594</v>
       </c>
     </row>
   </sheetData>
@@ -10411,7 +10422,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C910"/>
+  <dimension ref="A1:C911"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20422,6 +20433,17 @@
       </c>
       <c r="C910">
         <v>100.4989</v>
+      </c>
+    </row>
+    <row r="911" spans="1:3">
+      <c r="A911" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B911">
+        <v>1</v>
+      </c>
+      <c r="C911">
+        <v>99.2525</v>
       </c>
     </row>
   </sheetData>
@@ -20431,7 +20453,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C910"/>
+  <dimension ref="A1:C911"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -30442,6 +30464,17 @@
       </c>
       <c r="C910">
         <v>62.4162</v>
+      </c>
+    </row>
+    <row r="911" spans="1:3">
+      <c r="A911" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B911">
+        <v>1</v>
+      </c>
+      <c r="C911">
+        <v>61.8042</v>
       </c>
     </row>
   </sheetData>
@@ -30451,7 +30484,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C910"/>
+  <dimension ref="A1:C911"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -40462,6 +40495,17 @@
       </c>
       <c r="C910">
         <v>12.8842</v>
+      </c>
+    </row>
+    <row r="911" spans="1:3">
+      <c r="A911" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B911">
+        <v>1</v>
+      </c>
+      <c r="C911">
+        <v>12.7373</v>
       </c>
     </row>
   </sheetData>
@@ -40471,7 +40515,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C910"/>
+  <dimension ref="A1:C911"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -50482,6 +50526,17 @@
       </c>
       <c r="C910">
         <v>117.1277</v>
+      </c>
+    </row>
+    <row r="911" spans="1:3">
+      <c r="A911" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B911">
+        <v>1</v>
+      </c>
+      <c r="C911">
+        <v>115.8231</v>
       </c>
     </row>
   </sheetData>
@@ -50491,7 +50546,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C910"/>
+  <dimension ref="A1:C911"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -60502,6 +60557,17 @@
       </c>
       <c r="C910">
         <v>19.0339</v>
+      </c>
+    </row>
+    <row r="911" spans="1:3">
+      <c r="A911" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B911">
+        <v>100</v>
+      </c>
+      <c r="C911">
+        <v>18.8046</v>
       </c>
     </row>
   </sheetData>
@@ -60511,7 +60577,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C910"/>
+  <dimension ref="A1:C911"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -70522,6 +70588,17 @@
       </c>
       <c r="C910">
         <v>56.2609</v>
+      </c>
+    </row>
+    <row r="911" spans="1:3">
+      <c r="A911" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B911">
+        <v>100</v>
+      </c>
+      <c r="C911">
+        <v>55.5942</v>
       </c>
     </row>
   </sheetData>
@@ -70531,7 +70608,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C910"/>
+  <dimension ref="A1:C911"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -80544,6 +80621,17 @@
         <v>106.5201</v>
       </c>
     </row>
+    <row r="911" spans="1:3">
+      <c r="A911" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B911">
+        <v>1</v>
+      </c>
+      <c r="C911">
+        <v>105.5706</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C911"/>
+  <dimension ref="A1:C912"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10413,6 +10413,17 @@
       </c>
       <c r="C911">
         <v>85.4594</v>
+      </c>
+    </row>
+    <row r="912" spans="1:3">
+      <c r="A912" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B912">
+        <v>1</v>
+      </c>
+      <c r="C912">
+        <v>84.35080000000001</v>
       </c>
     </row>
   </sheetData>
@@ -10422,7 +10433,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C911"/>
+  <dimension ref="A1:C912"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20444,6 +20455,17 @@
       </c>
       <c r="C911">
         <v>99.2525</v>
+      </c>
+    </row>
+    <row r="912" spans="1:3">
+      <c r="A912" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B912">
+        <v>1</v>
+      </c>
+      <c r="C912">
+        <v>98.2856</v>
       </c>
     </row>
   </sheetData>
@@ -20453,7 +20475,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C911"/>
+  <dimension ref="A1:C912"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -30475,6 +30497,17 @@
       </c>
       <c r="C911">
         <v>61.8042</v>
+      </c>
+    </row>
+    <row r="912" spans="1:3">
+      <c r="A912" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B912">
+        <v>1</v>
+      </c>
+      <c r="C912">
+        <v>60.9013</v>
       </c>
     </row>
   </sheetData>
@@ -30484,7 +30517,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C911"/>
+  <dimension ref="A1:C912"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -40506,6 +40539,17 @@
       </c>
       <c r="C911">
         <v>12.7373</v>
+      </c>
+    </row>
+    <row r="912" spans="1:3">
+      <c r="A912" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B912">
+        <v>1</v>
+      </c>
+      <c r="C912">
+        <v>12.5637</v>
       </c>
     </row>
   </sheetData>
@@ -40515,7 +40559,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C911"/>
+  <dimension ref="A1:C912"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -50537,6 +50581,17 @@
       </c>
       <c r="C911">
         <v>115.8231</v>
+      </c>
+    </row>
+    <row r="912" spans="1:3">
+      <c r="A912" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B912">
+        <v>1</v>
+      </c>
+      <c r="C912">
+        <v>114.405</v>
       </c>
     </row>
   </sheetData>
@@ -50546,7 +50601,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C911"/>
+  <dimension ref="A1:C912"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -60568,6 +60623,17 @@
       </c>
       <c r="C911">
         <v>18.8046</v>
+      </c>
+    </row>
+    <row r="912" spans="1:3">
+      <c r="A912" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B912">
+        <v>100</v>
+      </c>
+      <c r="C912">
+        <v>18.4619</v>
       </c>
     </row>
   </sheetData>
@@ -60577,7 +60643,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C911"/>
+  <dimension ref="A1:C912"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -70599,6 +70665,17 @@
       </c>
       <c r="C911">
         <v>55.5942</v>
+      </c>
+    </row>
+    <row r="912" spans="1:3">
+      <c r="A912" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B912">
+        <v>100</v>
+      </c>
+      <c r="C912">
+        <v>54.8944</v>
       </c>
     </row>
   </sheetData>
@@ -70608,7 +70685,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C911"/>
+  <dimension ref="A1:C912"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -80632,6 +80709,17 @@
         <v>105.5706</v>
       </c>
     </row>
+    <row r="912" spans="1:3">
+      <c r="A912" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B912">
+        <v>1</v>
+      </c>
+      <c r="C912">
+        <v>104.0982</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C912"/>
+  <dimension ref="A1:C913"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10424,6 +10424,17 @@
       </c>
       <c r="C912">
         <v>84.35080000000001</v>
+      </c>
+    </row>
+    <row r="913" spans="1:3">
+      <c r="A913" s="2">
+        <v>46277</v>
+      </c>
+      <c r="B913">
+        <v>1</v>
+      </c>
+      <c r="C913">
+        <v>84.2569</v>
       </c>
     </row>
   </sheetData>
@@ -10433,7 +10444,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C912"/>
+  <dimension ref="A1:C913"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20466,6 +20477,17 @@
       </c>
       <c r="C912">
         <v>98.2856</v>
+      </c>
+    </row>
+    <row r="913" spans="1:3">
+      <c r="A913" s="2">
+        <v>46277</v>
+      </c>
+      <c r="B913">
+        <v>1</v>
+      </c>
+      <c r="C913">
+        <v>97.8728</v>
       </c>
     </row>
   </sheetData>
@@ -20475,7 +20497,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C912"/>
+  <dimension ref="A1:C913"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -30508,6 +30530,17 @@
       </c>
       <c r="C912">
         <v>60.9013</v>
+      </c>
+    </row>
+    <row r="913" spans="1:3">
+      <c r="A913" s="2">
+        <v>46277</v>
+      </c>
+      <c r="B913">
+        <v>1</v>
+      </c>
+      <c r="C913">
+        <v>60.429</v>
       </c>
     </row>
   </sheetData>
@@ -30517,7 +30550,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C912"/>
+  <dimension ref="A1:C913"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -40550,6 +40583,17 @@
       </c>
       <c r="C912">
         <v>12.5637</v>
+      </c>
+    </row>
+    <row r="913" spans="1:3">
+      <c r="A913" s="2">
+        <v>46277</v>
+      </c>
+      <c r="B913">
+        <v>1</v>
+      </c>
+      <c r="C913">
+        <v>12.5519</v>
       </c>
     </row>
   </sheetData>
@@ -40559,7 +40603,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C912"/>
+  <dimension ref="A1:C913"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -50592,6 +50636,17 @@
       </c>
       <c r="C912">
         <v>114.405</v>
+      </c>
+    </row>
+    <row r="913" spans="1:3">
+      <c r="A913" s="2">
+        <v>46277</v>
+      </c>
+      <c r="B913">
+        <v>1</v>
+      </c>
+      <c r="C913">
+        <v>114.008</v>
       </c>
     </row>
   </sheetData>
@@ -50601,7 +50656,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C912"/>
+  <dimension ref="A1:C913"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -60634,6 +60689,17 @@
       </c>
       <c r="C912">
         <v>18.4619</v>
+      </c>
+    </row>
+    <row r="913" spans="1:3">
+      <c r="A913" s="2">
+        <v>46277</v>
+      </c>
+      <c r="B913">
+        <v>100</v>
+      </c>
+      <c r="C913">
+        <v>18.6909</v>
       </c>
     </row>
   </sheetData>
@@ -60643,7 +60709,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C912"/>
+  <dimension ref="A1:C913"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -70676,6 +70742,17 @@
       </c>
       <c r="C912">
         <v>54.8944</v>
+      </c>
+    </row>
+    <row r="913" spans="1:3">
+      <c r="A913" s="2">
+        <v>46277</v>
+      </c>
+      <c r="B913">
+        <v>100</v>
+      </c>
+      <c r="C913">
+        <v>54.5035</v>
       </c>
     </row>
   </sheetData>
@@ -70685,7 +70762,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C912"/>
+  <dimension ref="A1:C913"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -80720,6 +80797,17 @@
         <v>104.0982</v>
       </c>
     </row>
+    <row r="913" spans="1:3">
+      <c r="A913" s="2">
+        <v>46277</v>
+      </c>
+      <c r="B913">
+        <v>1</v>
+      </c>
+      <c r="C913">
+        <v>103.4843</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
